--- a/Shiftwell_Step1_Analysis.xlsx
+++ b/Shiftwell_Step1_Analysis.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="108">
   <si>
     <t xml:space="preserve">Shiftwell – Step 1 analysis (all cells are live formulas)</t>
   </si>
@@ -57,6 +57,12 @@
     <t xml:space="preserve">Assumed 'today' = 16 Oct 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">At-risk ARR renewing Dec 2026 or later = reachable by this quarter's build (₹ lakh)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CarePoint + FreshBowl. FitZone and Brew &amp; Co renew before anything ships</t>
+  </si>
+  <si>
     <t xml:space="preserve">2. Swap approval rate vs health</t>
   </si>
   <si>
@@ -84,6 +90,9 @@
     <t xml:space="preserve">ARR in accounts with approval &lt;50% (₹ lakh)</t>
   </si>
   <si>
+    <t xml:space="preserve">Swap-volume-weighted approval: At risk (col B) / Healthy (col C)</t>
+  </si>
+  <si>
     <t xml:space="preserve">3. Manager time on scheduling</t>
   </si>
   <si>
@@ -150,6 +159,12 @@
     <t xml:space="preserve">…as % of FreshBowl ARR</t>
   </si>
   <si>
+    <t xml:space="preserve">FreshBowl WhatsApp cost if manager's 27.5 swaps/night applied to all 120 locations (₹ lakh/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare row 40 (app data). The real swap count would settle which is right</t>
+  </si>
+  <si>
     <t xml:space="preserve">6. Sprint budget (6 available)</t>
   </si>
   <si>
@@ -282,7 +297,7 @@
     <t xml:space="preserve">Check: ARR total should equal 408 lakh (₹4.08 Cr) per the brief.</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumption: renewal dates set to the 1st of the stated month (case gives month only).</t>
+    <t xml:space="preserve">Assumption: renewal dates set to the last day of the stated month (case gives month only).</t>
   </si>
   <si>
     <t xml:space="preserve">ARR lost (₹ lakh)</t>
@@ -929,22 +944,34 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">DATEDIF(DATE(2026,10,16),Accounts!E2,"m")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <f aca="false">SUMIFS(Accounts!D2:D9,Accounts!J2:J9,"At risk",Accounts!E2:E9,"&gt;="&amp;DATE(2026,12,1))</f>
+        <v>144</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" s="6" t="n">
         <f aca="false">AVERAGEIFS(Accounts!H2:H9,Accounts!J2:J9,"At risk")</f>
@@ -953,7 +980,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="6" t="n">
         <f aca="false">AVERAGEIFS(Accounts!H2:H9,Accounts!J2:J9,"Healthy")</f>
@@ -962,7 +989,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" s="6" t="n">
         <f aca="false">AVERAGEIFS(Accounts!H2:H9,Accounts!J2:J9,"Watch")</f>
@@ -971,7 +998,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" s="6" t="n">
         <f aca="false">Lost!F8</f>
@@ -980,7 +1007,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="5" t="n">
         <f aca="false">SUM(Accounts!O2:O9)</f>
@@ -989,19 +1016,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" s="5" t="n">
         <f aca="false">COUNTIFS(Accounts!O2:O9,1,Accounts!J2:J9,"&lt;&gt;Healthy")</f>
         <v>4</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" s="5" t="n">
         <f aca="false">SUMIFS(Accounts!D2:D9,Accounts!O2:O9,1)</f>
@@ -1017,16 +1044,29 @@
         <v>0.392156862745098</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <f aca="false">SUMPRODUCT((Accounts!J2:J9="At risk")*Accounts!G2:G9*Accounts!H2:H9)/SUMIFS(Accounts!G2:G9,Accounts!J2:J9,"At risk")</f>
+        <v>0.382691466083151</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <f aca="false">SUMPRODUCT((Accounts!J2:J9="Healthy")*Accounts!G2:G9*Accounts!H2:H9)/SUMIFS(Accounts!G2:G9,Accounts!J2:J9,"Healthy")</f>
+        <v>0.650596658711217</v>
+      </c>
+    </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B24" s="9" t="n">
         <f aca="false">AVERAGEIFS(Accounts!I2:I9,Accounts!J2:J9,"At risk")</f>
@@ -1035,7 +1075,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B25" s="9" t="n">
         <f aca="false">AVERAGEIFS(Accounts!I2:I9,Accounts!J2:J9,"Healthy")</f>
@@ -1044,38 +1084,38 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B26" s="10" t="n">
         <f aca="false">CORREL(Accounts!H2:H9,Accounts!I2:I9)</f>
         <v>-0.951254971383125</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B27" s="10" t="n">
         <f aca="false">CORREL(Accounts!H2:H9,Accounts!N2:N9)</f>
         <v>-0.543716720108588</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" s="9" t="n">
         <f aca="false">Accounts!K3</f>
@@ -1084,7 +1124,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" s="9" t="n">
         <f aca="false">Accounts!K2</f>
@@ -1093,7 +1133,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B32" s="9" t="n">
         <f aca="false">Accounts!K4</f>
@@ -1102,7 +1142,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B33" s="9" t="n">
         <f aca="false">Accounts!K9</f>
@@ -1111,7 +1151,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B34" s="9" t="n">
         <f aca="false">Accounts!G10/Accounts!C10</f>
@@ -1120,48 +1160,48 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B35" s="9" t="n">
         <f aca="false">Accounts!G3/Accounts!C3/30</f>
         <v>0.805555555555556</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B38" s="11" t="n">
         <v>0.35</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B40" s="10" t="n">
         <f aca="false">Accounts!G3*B39*B38*12/100000</f>
@@ -1170,23 +1210,35 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B41" s="13" t="n">
         <f aca="false">B40/(Accounts!D3)</f>
         <v>0.0058</v>
       </c>
     </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="9" t="n">
+        <f aca="false">27.5*Accounts!C3*30*B39*B38*12/100000</f>
+        <v>16.632</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B44" s="14" t="n">
         <v>6</v>
@@ -1194,7 +1246,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B45" s="14" t="n">
         <v>3</v>
@@ -1202,7 +1254,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B46" s="14" t="n">
         <v>2</v>
@@ -1210,7 +1262,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B47" s="14" t="n">
         <v>1</v>
@@ -1218,19 +1270,19 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B48" s="5" t="n">
         <f aca="false">SUM(B45:B47)</f>
         <v>6</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B49" s="5" t="n">
         <f aca="false">B44-B48</f>
@@ -1239,7 +1291,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1276,57 +1328,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M1" s="15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N1" s="15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C2" s="16" t="n">
         <v>200</v>
@@ -1335,7 +1387,7 @@
         <v>110</v>
       </c>
       <c r="E2" s="17" t="n">
-        <v>46600</v>
+        <v>46630</v>
       </c>
       <c r="F2" s="16" t="n">
         <v>5200</v>
@@ -1350,7 +1402,7 @@
         <v>3.5</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K2" s="19" t="n">
         <f aca="false">G2/C2</f>
@@ -1375,10 +1427,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C3" s="16" t="n">
         <v>120</v>
@@ -1387,7 +1439,7 @@
         <v>84</v>
       </c>
       <c r="E3" s="17" t="n">
-        <v>46388</v>
+        <v>46418</v>
       </c>
       <c r="F3" s="16" t="n">
         <v>3600</v>
@@ -1402,7 +1454,7 @@
         <v>6.5</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K3" s="19" t="n">
         <f aca="false">G3/C3</f>
@@ -1427,10 +1479,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>40</v>
@@ -1439,7 +1491,7 @@
         <v>60</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>46357</v>
+        <v>46387</v>
       </c>
       <c r="F4" s="16" t="n">
         <v>900</v>
@@ -1454,7 +1506,7 @@
         <v>4</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K4" s="19" t="n">
         <f aca="false">G4/C4</f>
@@ -1479,10 +1531,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>90</v>
@@ -1491,7 +1543,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>46539</v>
+        <v>46568</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>2100</v>
@@ -1506,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K5" s="19" t="n">
         <f aca="false">G5/C5</f>
@@ -1531,10 +1583,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>75</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>70</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>60</v>
@@ -1543,7 +1595,7 @@
         <v>36</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>46447</v>
+        <v>46477</v>
       </c>
       <c r="F6" s="16" t="n">
         <v>1500</v>
@@ -1558,7 +1610,7 @@
         <v>6</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="K6" s="19" t="n">
         <f aca="false">G6/C6</f>
@@ -1583,10 +1635,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>25</v>
@@ -1595,7 +1647,7 @@
         <v>30</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>46419</v>
+        <v>46446</v>
       </c>
       <c r="F7" s="16" t="n">
         <v>450</v>
@@ -1610,7 +1662,7 @@
         <v>2.5</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K7" s="19" t="n">
         <f aca="false">G7/C7</f>
@@ -1635,10 +1687,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>50</v>
@@ -1647,7 +1699,7 @@
         <v>22</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>46296</v>
+        <v>46326</v>
       </c>
       <c r="F8" s="16" t="n">
         <v>600</v>
@@ -1662,7 +1714,7 @@
         <v>5.5</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K8" s="19" t="n">
         <f aca="false">G8/C8</f>
@@ -1687,10 +1739,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>35</v>
@@ -1699,7 +1751,7 @@
         <v>18</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>46327</v>
+        <v>46356</v>
       </c>
       <c r="F9" s="16" t="n">
         <v>700</v>
@@ -1714,7 +1766,7 @@
         <v>7</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K9" s="19" t="n">
         <f aca="false">G9/C9</f>
@@ -1739,7 +1791,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">SUM(C2:C9)</f>
@@ -1760,12 +1812,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E13" s="22" t="str">
         <f aca="false">IF(D10=408,"OK","MISMATCH")</f>
@@ -1774,7 +1826,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1806,30 +1858,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C2" s="16" t="n">
         <v>70</v>
@@ -1838,7 +1890,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F2" s="18" t="n">
         <v>0.6</v>
@@ -1846,10 +1898,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C3" s="16" t="n">
         <v>45</v>
@@ -1858,7 +1910,7 @@
         <v>25</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>0.22</v>
@@ -1866,10 +1918,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C4" s="16" t="n">
         <v>30</v>
@@ -1878,7 +1930,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F4" s="18" t="n">
         <v>0.31</v>
@@ -1886,10 +1938,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>15</v>
@@ -1898,7 +1950,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>0.33</v>
@@ -1906,7 +1958,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D7" s="22" t="n">
         <f aca="false">SUM(D2:D5)</f>
@@ -1915,7 +1967,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F8" s="6" t="n">
         <f aca="false">AVERAGE(F2:F5)</f>
@@ -1924,7 +1976,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F9" s="22" t="str">
         <f aca="false">COUNTIF(F2:F5,"&lt;0.5")&amp;" of "&amp;COUNT(F2:F5)</f>
@@ -1933,7 +1985,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D10" s="22" t="n">
         <f aca="false">SUMIF(F2:F5,"&lt;0.5",D2:D5)</f>
@@ -1942,7 +1994,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D11" s="6" t="n">
         <f aca="false">D10/D7</f>
